--- a/S62aMigration/csv_and_xlsx_files/SS_data/S62A_Column_mapping.xlsx
+++ b/S62aMigration/csv_and_xlsx_files/SS_data/S62A_Column_mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abbas.merali/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nisalihalwathura/PINS/ODW-Service/odw-synapse-workspace/S62aMigration/csv_and_xlsx_files/SS_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B70578FC-99DC-354D-B6F4-30BC63408D94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5697B863-E762-5049-B57D-20CBEB3FA680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3680" yWindow="2240" windowWidth="18180" windowHeight="11500" xr2:uid="{12241D67-8D82-4829-AFAA-E70F395389D3}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="19780" xr2:uid="{12241D67-8D82-4829-AFAA-E70F395389D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Lookup" sheetId="5" r:id="rId1"/>
@@ -3405,10 +3405,10 @@
         <v>11</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>196</v>
+        <v>75</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>196</v>
+        <v>75</v>
       </c>
       <c r="G113" s="8" t="s">
         <v>8</v>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="I47">
         <f>MATCH(H47,Lookup!E:E,0)</f>
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="48" spans="4:9" x14ac:dyDescent="0.2">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="F49">
         <f>MATCH(E49,Lookup!D:D,0)</f>
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G49" t="s">
         <v>321</v>
@@ -6548,17 +6548,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3ac97f74-887d-4038-a207-790912953edc" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f1c51713-a7b9-4899-a01c-db85572982cc">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B674EA4B021E7B4197E0B77DCF8770A8" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ebb401e81e3712a12d23a789d2bfa9fe">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f1c51713-a7b9-4899-a01c-db85572982cc" xmlns:ns3="3ac97f74-887d-4038-a207-790912953edc" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3a6713f0e65e3bfee893efc160aaadb3" ns2:_="" ns3:_="">
     <xsd:import namespace="f1c51713-a7b9-4899-a01c-db85572982cc"/>
@@ -6765,6 +6754,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3ac97f74-887d-4038-a207-790912953edc" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f1c51713-a7b9-4899-a01c-db85572982cc">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA1644BE-8582-47DF-8F3F-89F5A20E96EE}">
   <ds:schemaRefs>
@@ -6774,23 +6774,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A53362A7-9112-4B9B-A76B-23EB85896A3D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="3ac97f74-887d-4038-a207-790912953edc"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="f1c51713-a7b9-4899-a01c-db85572982cc"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EAF8FBA-21F3-4051-8680-4ACAB3CDB416}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6807,4 +6790,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A53362A7-9112-4B9B-A76B-23EB85896A3D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="3ac97f74-887d-4038-a207-790912953edc"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f1c51713-a7b9-4899-a01c-db85572982cc"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>